--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484541_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484541_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.6024</v>
+        <v>7.3722</v>
       </c>
       <c r="E2" t="n">
-        <v>4.0497</v>
+        <v>4.6957</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5527</v>
+        <v>2.6765</v>
       </c>
       <c r="G2" t="n">
         <v>6.6163</v>
@@ -610,13 +610,13 @@
         <v>2.3823</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.8594</v>
+        <v>-1.0896</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.5965</v>
+        <v>-0.9506</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2629</v>
+        <v>-0.139</v>
       </c>
       <c r="V2" t="n">
         <v>2.212</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.0683</v>
+        <v>5.0931</v>
       </c>
       <c r="E3" t="n">
         <v>3.0211</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0473</v>
+        <v>2.072</v>
       </c>
       <c r="G3" t="n">
         <v>5.3317</v>
@@ -688,13 +688,13 @@
         <v>1.6493</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5695</v>
+        <v>-0.5447</v>
       </c>
       <c r="T3" t="n">
         <v>-0.6976</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1281</v>
+        <v>0.1529</v>
       </c>
       <c r="V3" t="n">
         <v>1.5889</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2025</v>
+        <v>2.7659</v>
       </c>
       <c r="E4" t="n">
-        <v>3.9125</v>
+        <v>3.5008</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7101</v>
+        <v>-0.7348</v>
       </c>
       <c r="G4" t="n">
         <v>3.7891</v>
@@ -766,13 +766,13 @@
         <v>0.9163</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6803</v>
+        <v>0.2438</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4744</v>
+        <v>0.0626</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2059</v>
+        <v>0.1812</v>
       </c>
       <c r="V4" t="n">
         <v>-1.267</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4203</v>
+        <v>2.6344</v>
       </c>
       <c r="E5" t="n">
-        <v>2.6197</v>
+        <v>2.9082</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1994</v>
+        <v>-0.2738</v>
       </c>
       <c r="G5" t="n">
         <v>3.589</v>
@@ -844,13 +844,13 @@
         <v>1.4661</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5797</v>
+        <v>-0.3656</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5875</v>
+        <v>-0.299</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0077</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="V5" t="n">
         <v>-0.9554</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.2923</v>
+        <v>2.0993</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2869</v>
+        <v>1.5894</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0054</v>
+        <v>0.5099</v>
       </c>
       <c r="G6" t="n">
         <v>1.9319</v>
@@ -922,13 +922,13 @@
         <v>1.4661</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3281</v>
+        <v>-0.5211</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.2111</v>
+        <v>-0.9087</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8831</v>
+        <v>0.3876</v>
       </c>
       <c r="V6" t="n">
         <v>0.3219</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3956</v>
+        <v>0.2965</v>
       </c>
       <c r="E8" t="n">
         <v>0.7085</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3128</v>
+        <v>-0.4119</v>
       </c>
       <c r="G8" t="n">
         <v>0.1864</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2092</v>
+        <v>0.1101</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2092</v>
+        <v>0.1101</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.805</v>
+        <v>-1.7555</v>
       </c>
       <c r="E9" t="n">
         <v>-0.0051</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.7999</v>
+        <v>-1.7504</v>
       </c>
       <c r="G9" t="n">
         <v>-0.1209</v>
@@ -1156,13 +1156,13 @@
         <v>0.3665</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4617</v>
+        <v>-0.4121</v>
       </c>
       <c r="T9" t="n">
         <v>-0.1101</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3516</v>
+        <v>-0.302</v>
       </c>
       <c r="V9" t="n">
         <v>-1.5889</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. DIAGNE</t>
+          <t>A. ALBA GONZALEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3384</v>
+        <v>-2.1964</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.0185</v>
+        <v>-4.5507</v>
       </c>
       <c r="F10" t="n">
-        <v>1.6801</v>
+        <v>2.3542</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0621</v>
+        <v>-1.6645</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2421</v>
+        <v>-3.1581</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3042</v>
+        <v>1.4936</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4793</v>
+        <v>-2.6301</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.0466</v>
+        <v>-2.8741</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.4327</v>
+        <v>0.244</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5413</v>
+        <v>0.9656</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1955</v>
+        <v>-0.284</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7368</v>
+        <v>1.2496</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.9321</v>
+        <v>1.0995</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.8484</v>
+        <v>-1.0995</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9163</v>
+        <v>2.1991</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5317</v>
+        <v>-0.6865</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3092</v>
+        <v>-0.8314</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2224</v>
+        <v>0.145</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.945</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.0104</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. ALBA GONZALEZ</t>
+          <t>C. FUSTER ROYO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4389</v>
+        <v>-2.555</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.6197</v>
+        <v>-2.6347</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1808</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.6645</v>
+        <v>-2.1356</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.1581</v>
+        <v>-1.9848</v>
       </c>
       <c r="I11" t="n">
-        <v>1.4936</v>
+        <v>-0.1508</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.6301</v>
+        <v>-1.5156</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.8741</v>
+        <v>-1.1087</v>
       </c>
       <c r="L11" t="n">
-        <v>0.244</v>
+        <v>-0.4069</v>
       </c>
       <c r="M11" t="n">
-        <v>0.9656</v>
+        <v>-0.6201</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.284</v>
+        <v>-0.8762</v>
       </c>
       <c r="O11" t="n">
-        <v>1.2496</v>
+        <v>0.2561</v>
       </c>
       <c r="P11" t="n">
-        <v>1.0995</v>
+        <v>0.5498</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.0995</v>
+        <v>-0.9163</v>
       </c>
       <c r="R11" t="n">
-        <v>2.1991</v>
+        <v>1.4661</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9288999999999999</v>
+        <v>-0.3252</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9004</v>
+        <v>-0.2029</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0285</v>
+        <v>-0.1224</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.945</v>
+        <v>-0.6439</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0104</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.9554</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C. FUSTER ROYO</t>
+          <t>E. DIAGNE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.3167</v>
+        <v>-2.8463</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.0744</v>
+        <v>-4.5264</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2423</v>
+        <v>1.6801</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.1356</v>
+        <v>0.0621</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.9848</v>
+        <v>-0.2421</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1508</v>
+        <v>0.3042</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.5156</v>
+        <v>-0.4793</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.1087</v>
+        <v>-0.0466</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.4069</v>
+        <v>-0.4327</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.6201</v>
+        <v>0.5413</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8762</v>
+        <v>-0.1955</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2561</v>
+        <v>0.7368</v>
       </c>
       <c r="P12" t="n">
-        <v>0.5498</v>
+        <v>-2.9321</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9163</v>
+        <v>-3.8484</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4661</v>
+        <v>0.9163</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0869</v>
+        <v>0.0237</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6425</v>
+        <v>-0.1987</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4444</v>
+        <v>0.2224</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.6439</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.6439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>11.3326</v>
+        <v>12.1584</v>
       </c>
       <c r="E13" t="n">
-        <v>5.1309</v>
+        <v>5.957000000000002</v>
       </c>
       <c r="F13" t="n">
-        <v>6.201799999999999</v>
+        <v>6.201499999999999</v>
       </c>
       <c r="G13" t="n">
         <v>18.8357</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.037599999999999</v>
+        <v>-1.0376</v>
       </c>
       <c r="I13" t="n">
         <v>19.8734</v>
@@ -1468,13 +1468,13 @@
         <v>12.8281</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.393000000000001</v>
+        <v>-3.5672</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.9621</v>
+        <v>-4.1364</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5689999999999998</v>
+        <v>0.5692</v>
       </c>
       <c r="V13" t="n">
         <v>-1.277399999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.7372</v>
+        <v>3.1616</v>
       </c>
       <c r="E14" t="n">
-        <v>3.524</v>
+        <v>3.0432</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2131</v>
+        <v>0.1184</v>
       </c>
       <c r="G14" t="n">
         <v>-1.5719</v>
@@ -1546,13 +1546,13 @@
         <v>2.7489</v>
       </c>
       <c r="S14" t="n">
-        <v>1.7201</v>
+        <v>1.1446</v>
       </c>
       <c r="T14" t="n">
-        <v>0.546</v>
+        <v>0.0653</v>
       </c>
       <c r="U14" t="n">
-        <v>1.1741</v>
+        <v>1.0793</v>
       </c>
       <c r="V14" t="n">
         <v>2.8559</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.7505</v>
+        <v>0.9272</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.0537</v>
+        <v>-0.5345</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8042</v>
+        <v>1.4618</v>
       </c>
       <c r="G15" t="n">
         <v>-2.9883</v>
@@ -1624,13 +1624,13 @@
         <v>2.3823</v>
       </c>
       <c r="S15" t="n">
-        <v>2.1787</v>
+        <v>1.3554</v>
       </c>
       <c r="T15" t="n">
-        <v>0.491</v>
+        <v>0.0102</v>
       </c>
       <c r="U15" t="n">
-        <v>1.6877</v>
+        <v>1.3452</v>
       </c>
       <c r="V15" t="n">
         <v>1.2774</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7059</v>
+        <v>0.7554999999999999</v>
       </c>
       <c r="E16" t="n">
         <v>0.105</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6009</v>
+        <v>0.6505</v>
       </c>
       <c r="G16" t="n">
         <v>0.4896</v>
@@ -1702,13 +1702,13 @@
         <v>0.1833</v>
       </c>
       <c r="S16" t="n">
-        <v>0.033</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0.033</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. ORTEGA IBAÑEZ</t>
+          <t>M. REOS CAMPOS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3251</v>
+        <v>0.6486</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3251</v>
+        <v>2.2311</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>-1.5825</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3251</v>
+        <v>2.419</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3251</v>
+        <v>1.954</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>0.4651</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3251</v>
+        <v>5.7012</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3251</v>
+        <v>3.0561</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.6452</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>-3.2822</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-1.1021</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>-2.1801</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-1.2828</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.9321</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.6493</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-0.1657</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>-0.5381</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>0.3723</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. REOS CAMPOS</t>
+          <t>A. ORTEGA IBAÑEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2766</v>
+        <v>0.3251</v>
       </c>
       <c r="E19" t="n">
-        <v>1.558</v>
+        <v>0.3251</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.8346</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>2.419</v>
+        <v>0.3251</v>
       </c>
       <c r="H19" t="n">
-        <v>1.954</v>
+        <v>0.3251</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4651</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>5.7012</v>
+        <v>0.3251</v>
       </c>
       <c r="K19" t="n">
-        <v>3.0561</v>
+        <v>0.3251</v>
       </c>
       <c r="L19" t="n">
-        <v>2.6452</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.2822</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1021</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.1801</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.2828</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.9321</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6493</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0909</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.2111</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1203</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0126</v>
+        <v>-2.2685</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0677</v>
+        <v>-2.1254</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0551</v>
+        <v>-0.1431</v>
       </c>
       <c r="G20" t="n">
         <v>-3.0502</v>
@@ -2014,13 +2014,13 @@
         <v>1.6493</v>
       </c>
       <c r="S20" t="n">
-        <v>2.8543</v>
+        <v>1.5984</v>
       </c>
       <c r="T20" t="n">
-        <v>1.6825</v>
+        <v>0.6248</v>
       </c>
       <c r="U20" t="n">
-        <v>1.1718</v>
+        <v>0.9736</v>
       </c>
       <c r="V20" t="n">
         <v>-0.6335</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. BERMEJO DORRONSORO</t>
+          <t>I. FRANCH RUIZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0389</v>
+        <v>-2.6085</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.2709</v>
+        <v>-1.8612</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7681</v>
+        <v>-0.7472</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.3535</v>
+        <v>-3.1609</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.8562</v>
+        <v>0.1568</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.4973</v>
+        <v>-3.3177</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.7844</v>
+        <v>-0.5351</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.8518</v>
+        <v>1.1796</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0674</v>
+        <v>-1.7147</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.5691</v>
+        <v>-2.6258</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0044</v>
+        <v>-1.0228</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.5647</v>
+        <v>-1.603</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1833</v>
+        <v>0.9163</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9163</v>
+        <v>-1.0995</v>
       </c>
       <c r="R21" t="n">
-        <v>1.0995</v>
+        <v>2.0158</v>
       </c>
       <c r="S21" t="n">
-        <v>1.1759</v>
+        <v>0.2696</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4744</v>
+        <v>-0.2266</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7015</v>
+        <v>0.4962</v>
       </c>
       <c r="V21" t="n">
-        <v>0.9554</v>
+        <v>-0.6335</v>
       </c>
       <c r="W21" t="n">
-        <v>0.9554</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.6335</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. FRANCH RUIZ</t>
+          <t>J. BERMEJO DORRONSORO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.5788</v>
+        <v>-2.6888</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.5343</v>
+        <v>-0.7516</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0445</v>
+        <v>-1.9371</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.1609</v>
+        <v>-4.3535</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1568</v>
+        <v>-1.8562</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.3177</v>
+        <v>-2.4973</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.5351</v>
+        <v>-0.7844</v>
       </c>
       <c r="K22" t="n">
-        <v>1.1796</v>
+        <v>-0.8518</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.7147</v>
+        <v>0.0674</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.6258</v>
+        <v>-3.5691</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.0228</v>
+        <v>-1.0044</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.603</v>
+        <v>-2.5647</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9163</v>
+        <v>0.1833</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.0995</v>
+        <v>-0.9163</v>
       </c>
       <c r="R22" t="n">
-        <v>2.0158</v>
+        <v>1.0995</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7007</v>
+        <v>0.526</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8997000000000001</v>
+        <v>-0.0064</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1989</v>
+        <v>0.5324</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.6335</v>
+        <v>0.9554</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.9554</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.6335</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.3144</v>
+        <v>-2.9507</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.5348</v>
+        <v>-3.7655</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2203</v>
+        <v>0.8149</v>
       </c>
       <c r="G23" t="n">
         <v>-1.9107</v>
@@ -2248,13 +2248,13 @@
         <v>2.5656</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0531</v>
+        <v>0.3107</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1018</v>
+        <v>-0.3325</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0487</v>
+        <v>0.6433</v>
       </c>
       <c r="V23" t="n">
         <v>-1.9005</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.2802</v>
+        <v>-6.6435</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.9025</v>
+        <v>-3.5179</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.3777</v>
+        <v>-3.1256</v>
       </c>
       <c r="G24" t="n">
         <v>-5.6842</v>
@@ -2326,13 +2326,13 @@
         <v>0.3665</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7244</v>
+        <v>-0.0877</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5505</v>
+        <v>-0.1659</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1738</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="V24" t="n">
         <v>-0.3219</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-11.3326</v>
+        <v>-10.6918</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.201599999999999</v>
+        <v>-6.2015</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.1313</v>
+        <v>-4.4899</v>
       </c>
       <c r="G25" t="n">
         <v>-18.8358</v>
@@ -2404,13 +2404,13 @@
         <v>14.6605</v>
       </c>
       <c r="S25" t="n">
-        <v>4.3929</v>
+        <v>5.0339</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5691999999999999</v>
+        <v>-0.5692</v>
       </c>
       <c r="U25" t="n">
-        <v>4.9622</v>
+        <v>5.6031</v>
       </c>
       <c r="V25" t="n">
         <v>1.2774</v>
